--- a/docs/03. 설계 - 엔티티_관계모형_기술서.xlsx
+++ b/docs/03. 설계 - 엔티티_관계모형_기술서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11013"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9523f8246e06aad/Data/프로젝트/제출문서양식/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imjonghyeon/Documents/ses/ses_project/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_583A8DDAC3356F22A0511D0DF2B2D25A411F9586" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F99C82-1956-4D3F-A8FA-26F63E28B454}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BDFFEB-D600-1441-8A2E-A842C80A54AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16000" yWindow="0" windowWidth="17600" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="제∙개정 이력서" sheetId="1" r:id="rId1"/>
@@ -23,21 +23,21 @@
     <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">도움말!$A$1:$J$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'엔티티 관계모형 기술서'!$A$1:$J$38</definedName>
     <definedName name="병">INDIRECT([1]자료!$B1)</definedName>
     <definedName name="분류">[2]워크자료!$A$2:$A$65536</definedName>
     <definedName name="찾기분류">INDIRECT([2]자료!$B1)</definedName>
     <definedName name="최">[1]워크자료!$A$2:$A$65536</definedName>
     <definedName name="최병">INDIRECT([1]자료!$B1)</definedName>
     <definedName name="최병호">INDIRECT([3]자료!$B1)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">도움말!$A$1:$J$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'엔티티 관계모형 기술서'!$A$1:$J$79</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="199">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -148,10 +148,6 @@
   </si>
   <si>
     <t>제약조건</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y/N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -362,12 +358,511 @@
     <t xml:space="preserve">제∙개정 이력 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>ㅋ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sulomon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임종현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">comment, post, survey, payment, point_withdrawal_request, email_verification, survey_response </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글, 게시물, 설문, 결제, 포인트 출금 요청, 이메일 인증, 설문 응답</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 정보 및 인증을 관리하는 테이블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_num</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>password</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>email</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>birthday</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>social_login</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_email_verified</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>phone_number</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BINARY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>points</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>created_at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>updated_at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP(6)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP(6) ON UPDATE CURRENT_TIMESTAMP(6)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PENDING'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>email_verification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일 인증</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일 인증 정보와 관련된 데이터를 관리하는 테이블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>verification_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>verification_code</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_verified</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>expiration_time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUTO_INCREMENT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>survey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사 정보, 참여자, 포인트, 상태 등을 관리하는 테이블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>survey_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>title</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>form_type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>participants</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>participant_limit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>startdate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enddate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>site_form'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>draft'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>survey_question</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문 질문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사에 포함된 질문과 관련된 정보를 저장하는 테이블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>question_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>question_text</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>question_type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSON</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>survey_response</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문 응답</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>survey, user</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사, 사용자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사에 대한 사용자 응답 정보를 관리하는 테이블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>response_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reponses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIMESTMAP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRERRENT_TIMESTAMP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>post</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user, survey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자, 설문조사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글 정보를 관리하며, 설문조사와 연결 가능하도록 구성된 테이블</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>post_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>content</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>category</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>views</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>image_path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>visibility</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>private_password</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>visible'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>payment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제 정보를 관리하는 테이블로, 결제 수단, 금액, 상태 등을 저장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>payment_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>amount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>payment_method</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(10, 2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pending'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>point_withdrawal_request</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포인트 인출 요청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포인트 인출 요청과 관련된 정보를 관리하는 테이블로, 요청 금액, 은행명, 계좌번호 등을 저장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdrawal_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>requested_amount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bank_name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>account_number</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>processed_at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>notice_id</t>
+  </si>
+  <si>
+    <t>admin_num</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>comment_id</t>
+  </si>
+  <si>
+    <t>post_id</t>
+  </si>
+  <si>
+    <t>user_num</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>notice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공지사항</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공지사항 정보를 관리하는 테이블로, 제목, 내용, 작성자 정보 등을 저장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>post, user</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글, 사용자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 정보를 관리하는 테이블로, 댓글 작성자, 게시글 정보, 상태 등을 저장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘active’</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사 및 게시판 ERD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sulomon_ERD_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -429,14 +924,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -483,6 +970,19 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -516,7 +1016,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -695,17 +1195,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -722,15 +1211,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -899,14 +1379,118 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -941,7 +1525,7 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -949,24 +1533,41 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1004,100 +1605,103 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1106,11 +1710,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1128,6 +1736,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1997720</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>167582</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{885171DE-3773-4658-C6E7-E670431C7BCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="165100" y="1701800"/>
+          <a:ext cx="7772400" cy="8752782"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1539,14 +2202,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="16.7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.7890625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.7890625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="10.7890625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.89453125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.1015625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.89453125" style="2"/>
+    <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="10.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.1640625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1557,17 +2220,17 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="21">
-      <c r="A2" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-    </row>
-    <row r="3" spans="1:6" ht="17" thickBot="1">
+    <row r="2" spans="1:6" ht="20">
+      <c r="A2" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" thickBot="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1588,138 +2251,138 @@
       <c r="D4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="27"/>
-    </row>
-    <row r="5" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="F4" s="34"/>
+    </row>
+    <row r="5" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-    </row>
-    <row r="6" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+    </row>
+    <row r="6" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-    </row>
-    <row r="8" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+    </row>
+    <row r="8" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-    </row>
-    <row r="9" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-    </row>
-    <row r="10" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+    </row>
+    <row r="10" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-    </row>
-    <row r="11" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+    </row>
+    <row r="11" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-    </row>
-    <row r="12" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-    </row>
-    <row r="13" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+    </row>
+    <row r="13" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-    </row>
-    <row r="14" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+    </row>
+    <row r="14" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-    </row>
-    <row r="15" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+    </row>
+    <row r="15" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-    </row>
-    <row r="16" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+    </row>
+    <row r="16" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-    </row>
-    <row r="17" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-    </row>
-    <row r="18" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+    </row>
+    <row r="18" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-    </row>
-    <row r="19" spans="1:6" s="5" customFormat="1" ht="15.35">
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+    </row>
+    <row r="19" spans="1:6" s="5" customFormat="1" ht="15">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-    </row>
-    <row r="20" spans="1:6" s="5" customFormat="1" ht="15.7" thickBot="1">
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="1:6" s="5" customFormat="1" ht="16" thickBot="1">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1755,564 +2418,4235 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <dimension ref="A1:M193"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.7890625" customWidth="1"/>
-    <col min="2" max="5" width="7.7890625" customWidth="1"/>
-    <col min="6" max="6" width="8.7890625" customWidth="1"/>
-    <col min="7" max="10" width="7.7890625" customWidth="1"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="63.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="60"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.7">
+    <row r="1" spans="1:13" ht="30" customHeight="1">
+      <c r="A1" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="66"/>
+    </row>
+    <row r="2" spans="1:13" ht="17">
       <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="B2" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
       <c r="F2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="61"/>
-    </row>
-    <row r="3" spans="1:10" ht="17" thickBot="1">
+      <c r="G2" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="67"/>
+    </row>
+    <row r="3" spans="1:13" ht="18" thickBot="1">
       <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
       <c r="F3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="G3" s="69">
+        <v>45590</v>
+      </c>
+      <c r="H3" s="70"/>
       <c r="I3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-    </row>
-    <row r="6" spans="1:10" ht="16.7">
-      <c r="A6" s="38" t="s">
+      <c r="J3" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:13" ht="17">
+      <c r="A6" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="16.7">
-      <c r="A7" s="52" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+    </row>
+    <row r="7" spans="1:13" ht="17">
+      <c r="A7" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="52" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="54"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="54"/>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1">
-      <c r="A8" s="43"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" s="61"/>
+      <c r="J7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1">
+      <c r="A8" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
       <c r="J8" s="45"/>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1">
-      <c r="A9" s="46"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="48"/>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="48"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="46"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="48"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="48"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="46"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="46"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="48"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="48"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="46"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="48"/>
-    </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A17" s="46"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="48"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="46"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="48"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="46"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="48"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="46"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="48"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="48"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="46"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="48"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="46"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="48"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="46"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="48"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="46"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="48"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="46"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="48"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="46"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="48"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="51"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-    </row>
-    <row r="31" spans="1:10" ht="16.7">
-      <c r="A31" s="32" t="s">
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="46"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1">
+      <c r="A9" s="47"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="48"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1">
+      <c r="A10" s="47"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="48"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="47"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="48"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="47"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="48"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="47"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="48"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="47"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="48"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="47"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="48"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="47"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="48"/>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1">
+      <c r="A17" s="47"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="48"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="47"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="48"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="47"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="48"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="47"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="48"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="47"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="48"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="47"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="48"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="47"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="48"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="47"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="48"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="47"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="48"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="47"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="48"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="47"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="48"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="47"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="48"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="47"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="48"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="47"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="48"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="47"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="48"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="47"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="48"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="47"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="48"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="47"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="48"/>
+    </row>
+    <row r="35" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A35" s="47"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="48"/>
+    </row>
+    <row r="36" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A36" s="47"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="48"/>
+    </row>
+    <row r="37" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A37" s="47"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="48"/>
+    </row>
+    <row r="38" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A38" s="47"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="48"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="47"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="48"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="47"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="48"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="47"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="48"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="47"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="48"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="47"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="48"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="47"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="48"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="47"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
+      <c r="M45" s="48"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="47"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="48"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="47"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
+      <c r="M47" s="48"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="47"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="48"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="47"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
+      <c r="M49" s="48"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="47"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="48"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="47"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="48"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="47"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="48"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="47"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="43"/>
+      <c r="M53" s="48"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="47"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+      <c r="L54" s="43"/>
+      <c r="M54" s="48"/>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="47"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+      <c r="L55" s="43"/>
+      <c r="M55" s="48"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="49"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="50"/>
+      <c r="L56" s="50"/>
+      <c r="M56" s="51"/>
+    </row>
+    <row r="59" spans="1:13" ht="17">
+      <c r="A59" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-    </row>
-    <row r="32" spans="1:10" ht="16.7">
-      <c r="A32" s="30" t="s">
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+    </row>
+    <row r="60" spans="1:13" ht="17">
+      <c r="A60" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="30" t="s">
+      <c r="B60" s="37"/>
+      <c r="C60" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G32" s="30"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-    </row>
-    <row r="33" spans="1:10" ht="16.7">
-      <c r="A33" s="30" t="s">
+      <c r="G60" s="37"/>
+      <c r="H60" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+    </row>
+    <row r="61" spans="1:13" ht="17">
+      <c r="A61" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="30" t="s">
+      <c r="B61" s="37"/>
+      <c r="C61" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.7">
-      <c r="A34" s="30" t="s">
+      <c r="G61" s="37"/>
+      <c r="H61" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+    </row>
+    <row r="62" spans="1:13" ht="17">
+      <c r="A62" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-    </row>
-    <row r="35" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="B62" s="37"/>
+      <c r="C62" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+    </row>
+    <row r="63" spans="1:13" ht="17">
+      <c r="A63" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B63" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C63" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D63" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E63" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F63" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G63" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H63" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I63" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="J63" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-    </row>
-    <row r="37" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-    </row>
-    <row r="38" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
+    <row r="64" spans="1:13" ht="17">
+      <c r="A64" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" s="19"/>
+      <c r="C64" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="20">
+        <v>16</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G64" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="17">
+      <c r="A65" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" s="19"/>
+      <c r="C65" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" s="19">
+        <v>255</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I65" s="19"/>
+      <c r="J65" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="17">
+      <c r="A66" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="19">
+        <v>255</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="17">
+      <c r="A67" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" s="19">
+        <v>255</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I67" s="19"/>
+      <c r="J67" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="17">
+      <c r="A68" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="19">
+        <v>255</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G68" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H68" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I68" s="19"/>
+      <c r="J68" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="17">
+      <c r="A69" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" s="19"/>
+      <c r="C69" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" s="19"/>
+      <c r="E69" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H69" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I69" s="19"/>
+      <c r="J69" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="17">
+      <c r="A70" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70" s="19"/>
+      <c r="C70" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D70" s="19">
+        <v>10</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H70" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I70" s="19"/>
+      <c r="J70" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="17">
+      <c r="A71" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" s="19"/>
+      <c r="C71" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="19"/>
+      <c r="E71" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I71" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="17">
+      <c r="A72" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="19"/>
+      <c r="C72" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" s="19">
+        <v>30</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G72" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="17">
+      <c r="A73" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" s="19"/>
+      <c r="C73" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="19"/>
+      <c r="E73" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I73" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="17">
+      <c r="A74" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="19">
+        <v>30</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I74" s="19"/>
+      <c r="J74" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="17">
+      <c r="A75" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" s="19"/>
+      <c r="E75" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H75" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I75" s="19">
+        <v>0</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="17">
+      <c r="A76" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="19">
+        <v>6</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H76" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J76" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="17">
+      <c r="A77" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="19"/>
+      <c r="C77" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" s="19">
+        <v>6</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F77" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G77" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H77" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I77" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J77" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="17">
+      <c r="A78" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="19"/>
+      <c r="C78" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="19">
+        <v>30</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I78" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="J78" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="17">
+      <c r="A80" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="43"/>
+      <c r="H80" s="43"/>
+      <c r="I80" s="43"/>
+      <c r="J80" s="43"/>
+    </row>
+    <row r="81" spans="1:10" ht="17">
+      <c r="A81" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" s="37"/>
+      <c r="C81" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="37"/>
+      <c r="H81" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+    </row>
+    <row r="82" spans="1:10" ht="17">
+      <c r="A82" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" s="37"/>
+      <c r="C82" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="37"/>
+      <c r="H82" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+    </row>
+    <row r="83" spans="1:10" ht="17">
+      <c r="A83" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" s="37"/>
+      <c r="C83" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="38"/>
+      <c r="J83" s="38"/>
+    </row>
+    <row r="84" spans="1:10" ht="17">
+      <c r="A84" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J84" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="17">
+      <c r="A85" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B85" s="19"/>
+      <c r="C85" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D85" s="19"/>
+      <c r="E85" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H85" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I85" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J85" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="17">
+      <c r="A86" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B86" s="19"/>
+      <c r="C86" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" s="19">
+        <v>16</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H86" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I86" s="19"/>
+      <c r="J86" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="17">
+      <c r="A87" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" s="19"/>
+      <c r="C87" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" s="19">
+        <v>255</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H87" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I87" s="19"/>
+      <c r="J87" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="17">
+      <c r="A88" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B88" s="19"/>
+      <c r="C88" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" s="19"/>
+      <c r="E88" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H88" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I88" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="17">
+      <c r="A89" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89" s="19"/>
+      <c r="C89" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="19">
+        <v>6</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H89" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I89" s="19"/>
+      <c r="J89" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="17">
+      <c r="A90" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="19"/>
+      <c r="C90" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90" s="19">
+        <v>6</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H90" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I90" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J90" s="20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="17">
+      <c r="A92" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" s="37"/>
+      <c r="C92" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="37"/>
+      <c r="H92" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="I92" s="38"/>
+      <c r="J92" s="38"/>
+    </row>
+    <row r="93" spans="1:10" ht="17">
+      <c r="A93" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" s="37"/>
+      <c r="C93" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" s="37"/>
+      <c r="H93" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I93" s="38"/>
+      <c r="J93" s="38"/>
+    </row>
+    <row r="94" spans="1:10" ht="17">
+      <c r="A94" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94" s="37"/>
+      <c r="C94" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="38"/>
+      <c r="J94" s="38"/>
+    </row>
+    <row r="95" spans="1:10" ht="17">
+      <c r="A95" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B95" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J95" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="17">
+      <c r="A96" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B96" s="19"/>
+      <c r="C96" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D96" s="19"/>
+      <c r="E96" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F96" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G96" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H96" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="I96" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J96" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="17">
+      <c r="A97" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D97" s="19">
+        <v>16</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F97" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G97" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H97" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I97" s="19"/>
+      <c r="J97" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="17">
+      <c r="A98" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B98" s="19"/>
+      <c r="C98" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D98" s="19">
+        <v>255</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F98" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H98" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I98" s="19"/>
+      <c r="J98" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="17">
+      <c r="A99" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B99" s="19"/>
+      <c r="C99" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D99" s="19"/>
+      <c r="E99" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G99" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H99" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I99" s="19"/>
+      <c r="J99" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="17">
+      <c r="A100" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" s="19"/>
+      <c r="C100" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D100" s="19">
+        <v>20</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G100" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H100" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I100" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="J100" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="17">
+      <c r="A101" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B101" s="19"/>
+      <c r="C101" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D101" s="19">
+        <v>255</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G101" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H101" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I101" s="19">
+        <v>0</v>
+      </c>
+      <c r="J101" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="17">
+      <c r="A102" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B102" s="19"/>
+      <c r="C102" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D102" s="19">
+        <v>255</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F102" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H102" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I102" s="19">
+        <v>0</v>
+      </c>
+      <c r="J102" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="17">
+      <c r="A103" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="19"/>
+      <c r="C103" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="D103" s="27">
+        <v>255</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F103" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G103" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="H103" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="I103">
+        <v>10</v>
+      </c>
+      <c r="J103" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="17">
+      <c r="A104" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B104" s="19"/>
+      <c r="C104" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D104" s="19">
+        <v>20</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F104" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G104" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H104" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="I104" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="J104" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="17">
+      <c r="A105" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B105" s="19"/>
+      <c r="C105" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105" s="19">
+        <v>6</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H105" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I105" s="19"/>
+      <c r="J105" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="17">
+      <c r="A106" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B106" s="19"/>
+      <c r="C106" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D106" s="19">
+        <v>6</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F106" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G106" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H106" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I106" s="19"/>
+      <c r="J106" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="17">
+      <c r="A107" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B107" s="19"/>
+      <c r="C107" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107" s="19">
+        <v>6</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F107" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G107" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H107" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I107" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J107" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="17">
+      <c r="A108" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B108" s="19"/>
+      <c r="C108" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" s="19">
+        <v>6</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F108" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G108" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H108" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I108" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J108" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="17">
+      <c r="A110" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" s="37"/>
+      <c r="C110" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="D110" s="38"/>
+      <c r="E110" s="38"/>
+      <c r="F110" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" s="37"/>
+      <c r="H110" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="I110" s="38"/>
+      <c r="J110" s="38"/>
+    </row>
+    <row r="111" spans="1:10" ht="17">
+      <c r="A111" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" s="37"/>
+      <c r="C111" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" s="38"/>
+      <c r="E111" s="38"/>
+      <c r="F111" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" s="37"/>
+      <c r="H111" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="I111" s="38"/>
+      <c r="J111" s="38"/>
+    </row>
+    <row r="112" spans="1:10" ht="17">
+      <c r="A112" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B112" s="37"/>
+      <c r="C112" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="D112" s="38"/>
+      <c r="E112" s="38"/>
+      <c r="F112" s="38"/>
+      <c r="G112" s="38"/>
+      <c r="H112" s="38"/>
+      <c r="I112" s="38"/>
+      <c r="J112" s="38"/>
+    </row>
+    <row r="113" spans="1:10" ht="17">
+      <c r="A113" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E113" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F113" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I113" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J113" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="17">
+      <c r="A114" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B114" s="19"/>
+      <c r="C114" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D114" s="19"/>
+      <c r="E114" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F114" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G114" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H114" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I114" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J114" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="17">
+      <c r="A115" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115" s="19"/>
+      <c r="C115" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D115" s="19"/>
+      <c r="E115" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F115" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G115" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H115" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I115" s="19"/>
+      <c r="J115" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="17">
+      <c r="A116" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B116" s="19"/>
+      <c r="C116" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D116" s="19"/>
+      <c r="E116" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F116" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G116" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H116" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I116" s="19"/>
+      <c r="J116" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="17">
+      <c r="A117" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B117" s="19"/>
+      <c r="C117" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D117" s="19">
+        <v>50</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G117" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H117" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I117" s="19"/>
+      <c r="J117" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="17">
+      <c r="A118" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B118" s="19"/>
+      <c r="C118" s="81" t="s">
+        <v>137</v>
+      </c>
+      <c r="D118" s="19"/>
+      <c r="E118" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F118" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G118" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I118" s="19"/>
+      <c r="J118" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="17">
+      <c r="A120" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B120" s="37"/>
+      <c r="C120" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D120" s="38"/>
+      <c r="E120" s="38"/>
+      <c r="F120" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" s="37"/>
+      <c r="H120" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="I120" s="38"/>
+      <c r="J120" s="38"/>
+    </row>
+    <row r="121" spans="1:10" ht="17">
+      <c r="A121" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" s="37"/>
+      <c r="C121" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D121" s="38"/>
+      <c r="E121" s="38"/>
+      <c r="F121" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="37"/>
+      <c r="H121" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="I121" s="38"/>
+      <c r="J121" s="38"/>
+    </row>
+    <row r="122" spans="1:10" ht="17">
+      <c r="A122" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B122" s="37"/>
+      <c r="C122" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D122" s="38"/>
+      <c r="E122" s="38"/>
+      <c r="F122" s="38"/>
+      <c r="G122" s="38"/>
+      <c r="H122" s="38"/>
+      <c r="I122" s="38"/>
+      <c r="J122" s="38"/>
+    </row>
+    <row r="123" spans="1:10" ht="17">
+      <c r="A123" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D123" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F123" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I123" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J123" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="17">
+      <c r="A124" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124" s="19"/>
+      <c r="C124" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D124" s="19"/>
+      <c r="E124" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F124" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G124" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H124" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I124" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J124" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="17">
+      <c r="A125" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B125" s="19"/>
+      <c r="C125" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D125" s="19"/>
+      <c r="E125" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F125" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G125" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H125" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I125" s="19"/>
+      <c r="J125" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="17">
+      <c r="A126" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B126" s="19"/>
+      <c r="C126" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D126" s="19">
+        <v>16</v>
+      </c>
+      <c r="E126" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F126" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G126" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H126" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I126" s="19"/>
+      <c r="J126" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="17">
+      <c r="A127" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" s="19"/>
+      <c r="C127" s="81" t="s">
+        <v>137</v>
+      </c>
+      <c r="D127" s="19"/>
+      <c r="E127" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F127" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I127" s="19"/>
+      <c r="J127" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="17">
+      <c r="A128" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B128" s="19"/>
+      <c r="C128" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="D128" s="19">
+        <v>6</v>
+      </c>
+      <c r="E128" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F128" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G128" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H128" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I128" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="J128" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="17">
+      <c r="A130" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B130" s="37"/>
+      <c r="C130" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D130" s="38"/>
+      <c r="E130" s="38"/>
+      <c r="F130" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" s="37"/>
+      <c r="H130" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I130" s="38"/>
+      <c r="J130" s="38"/>
+    </row>
+    <row r="131" spans="1:10" ht="17">
+      <c r="A131" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="37"/>
+      <c r="C131" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="D131" s="38"/>
+      <c r="E131" s="38"/>
+      <c r="F131" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" s="37"/>
+      <c r="H131" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="I131" s="38"/>
+      <c r="J131" s="38"/>
+    </row>
+    <row r="132" spans="1:10" ht="17">
+      <c r="A132" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B132" s="37"/>
+      <c r="C132" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="D132" s="38"/>
+      <c r="E132" s="38"/>
+      <c r="F132" s="38"/>
+      <c r="G132" s="38"/>
+      <c r="H132" s="38"/>
+      <c r="I132" s="38"/>
+      <c r="J132" s="38"/>
+    </row>
+    <row r="133" spans="1:10" ht="17">
+      <c r="A133" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E133" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F133" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G133" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H133" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I133" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J133" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="17">
+      <c r="A134" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B134" s="19"/>
+      <c r="C134" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D134" s="19"/>
+      <c r="E134" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F134" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G134" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H134" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I134" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J134" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="17">
+      <c r="A135" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B135" s="19"/>
+      <c r="C135" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D135" s="19"/>
+      <c r="E135" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F135" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G135" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H135" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I135" s="19"/>
+      <c r="J135" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="17">
+      <c r="A136" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B136" s="19"/>
+      <c r="C136" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D136" s="19">
+        <v>16</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F136" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G136" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I136" s="19"/>
+      <c r="J136" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="17">
+      <c r="A137" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B137" s="19"/>
+      <c r="C137" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D137" s="19">
+        <v>255</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F137" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G137" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H137" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I137" s="19"/>
+      <c r="J137" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="17">
+      <c r="A138" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B138" s="19"/>
+      <c r="C138" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D138" s="19"/>
+      <c r="E138" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F138" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G138" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H138" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I138" s="19"/>
+      <c r="J138" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="17">
+      <c r="A139" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B139" s="19"/>
+      <c r="C139" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D139" s="19">
+        <v>50</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F139" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G139" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H139" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I139" s="19"/>
+      <c r="J139" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="17">
+      <c r="A140" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B140" s="19"/>
+      <c r="C140" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D140" s="19"/>
+      <c r="E140" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F140" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G140" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H140" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I140" s="19">
+        <v>0</v>
+      </c>
+      <c r="J140" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="17">
+      <c r="A141" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B141" s="19"/>
+      <c r="C141" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D141" s="19">
+        <v>255</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G141" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J141" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="17">
+      <c r="A142" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B142" s="19"/>
+      <c r="C142" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D142" s="19">
+        <v>10</v>
+      </c>
+      <c r="E142" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F142" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G142" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H142" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I142" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="J142" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="17">
+      <c r="A143" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="B143" s="19"/>
+      <c r="C143" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D143" s="19">
+        <v>255</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G143" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H143" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J143" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="17">
+      <c r="A144" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B144" s="19"/>
+      <c r="C144" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D144" s="19">
+        <v>6</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F144" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G144" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H144" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I144" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J144" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="17">
+      <c r="A145" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B145" s="19"/>
+      <c r="C145" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D145" s="19">
+        <v>6</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F145" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G145" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H145" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I145" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J145" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="17">
+      <c r="A146" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B146" s="19"/>
+      <c r="C146" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D146" s="19">
+        <v>10</v>
+      </c>
+      <c r="E146" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F146" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G146" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H146" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I146" s="19"/>
+      <c r="J146" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="17">
+      <c r="A148" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B148" s="37"/>
+      <c r="C148" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D148" s="38"/>
+      <c r="E148" s="38"/>
+      <c r="F148" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="37"/>
+      <c r="H148" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I148" s="38"/>
+      <c r="J148" s="38"/>
+    </row>
+    <row r="149" spans="1:10" ht="17">
+      <c r="A149" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="37"/>
+      <c r="C149" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D149" s="38"/>
+      <c r="E149" s="38"/>
+      <c r="F149" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G149" s="37"/>
+      <c r="H149" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I149" s="38"/>
+      <c r="J149" s="38"/>
+    </row>
+    <row r="150" spans="1:10" ht="17">
+      <c r="A150" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B150" s="37"/>
+      <c r="C150" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D150" s="38"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="38"/>
+    </row>
+    <row r="151" spans="1:10" ht="17">
+      <c r="A151" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C151" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E151" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H151" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I151" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J151" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="17">
+      <c r="A152" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B152" s="19"/>
+      <c r="C152" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D152" s="19"/>
+      <c r="E152" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F152" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G152" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H152" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I152" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J152" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="17">
+      <c r="A153" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B153" s="19"/>
+      <c r="C153" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D153" s="19">
+        <v>16</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F153" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G153" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H153" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I153" s="19"/>
+      <c r="J153" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="17">
+      <c r="A154" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B154" s="19"/>
+      <c r="C154" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D154" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E154" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F154" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G154" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H154" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I154" s="19"/>
+      <c r="J154" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="17">
+      <c r="A155" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B155" s="19"/>
+      <c r="C155" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D155" s="19">
+        <v>20</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F155" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G155" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H155" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I155" s="19"/>
+      <c r="J155" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="17">
+      <c r="A156" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B156" s="19"/>
+      <c r="C156" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D156" s="19">
+        <v>20</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F156" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G156" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H156" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I156" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="J156" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="17">
+      <c r="A157" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B157" s="19"/>
+      <c r="C157" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D157" s="19">
+        <v>6</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G157" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H157" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I157" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J157" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="17">
+      <c r="A159" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B159" s="37"/>
+      <c r="C159" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D159" s="38"/>
+      <c r="E159" s="38"/>
+      <c r="F159" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" s="37"/>
+      <c r="H159" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="I159" s="38"/>
+      <c r="J159" s="38"/>
+    </row>
+    <row r="160" spans="1:10" ht="17">
+      <c r="A160" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" s="37"/>
+      <c r="C160" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D160" s="38"/>
+      <c r="E160" s="38"/>
+      <c r="F160" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G160" s="37"/>
+      <c r="H160" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I160" s="38"/>
+      <c r="J160" s="38"/>
+    </row>
+    <row r="161" spans="1:10" ht="17">
+      <c r="A161" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B161" s="37"/>
+      <c r="C161" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="D161" s="38"/>
+      <c r="E161" s="38"/>
+      <c r="F161" s="38"/>
+      <c r="G161" s="38"/>
+      <c r="H161" s="38"/>
+      <c r="I161" s="38"/>
+      <c r="J161" s="38"/>
+    </row>
+    <row r="162" spans="1:10" ht="17">
+      <c r="A162" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C162" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E162" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G162" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H162" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I162" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J162" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="17">
+      <c r="A163" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B163" s="19"/>
+      <c r="C163" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D163" s="19"/>
+      <c r="E163" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F163" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G163" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H163" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I163" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J163" s="19"/>
+    </row>
+    <row r="164" spans="1:10" ht="17">
+      <c r="A164" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B164" s="19"/>
+      <c r="C164" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D164" s="19">
+        <v>16</v>
+      </c>
+      <c r="E164" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F164" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G164" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H164" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I164" s="19"/>
+      <c r="J164" s="19"/>
+    </row>
+    <row r="165" spans="1:10" ht="17">
+      <c r="A165" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B165" s="19"/>
+      <c r="C165" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D165" s="19"/>
+      <c r="E165" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F165" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G165" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H165" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I165" s="19"/>
+      <c r="J165" s="19"/>
+    </row>
+    <row r="166" spans="1:10" ht="17">
+      <c r="A166" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B166" s="19"/>
+      <c r="C166" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D166" s="19">
+        <v>100</v>
+      </c>
+      <c r="E166" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F166" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G166" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H166" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I166" s="19"/>
+      <c r="J166" s="19"/>
+    </row>
+    <row r="167" spans="1:10" ht="17">
+      <c r="A167" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B167" s="19"/>
+      <c r="C167" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D167" s="80">
+        <v>50</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F167" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G167" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H167" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I167" s="19"/>
+      <c r="J167" s="19"/>
+    </row>
+    <row r="168" spans="1:10" ht="17">
+      <c r="A168" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B168" s="19"/>
+      <c r="C168" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D168" s="19">
+        <v>20</v>
+      </c>
+      <c r="E168" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F168" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G168" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H168" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I168" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="J168" s="19"/>
+    </row>
+    <row r="169" spans="1:10" ht="17">
+      <c r="A169" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B169" s="19"/>
+      <c r="C169" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D169" s="19">
+        <v>6</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F169" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G169" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H169" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I169" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J169" s="19"/>
+    </row>
+    <row r="170" spans="1:10" ht="17">
+      <c r="A170" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" s="19"/>
+      <c r="C170" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D170" s="19">
+        <v>6</v>
+      </c>
+      <c r="E170" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F170" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G170" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H170" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I170" s="19"/>
+      <c r="J170" s="19"/>
+    </row>
+    <row r="172" spans="1:10" ht="17">
+      <c r="A172" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B172" s="37"/>
+      <c r="C172" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D172" s="38"/>
+      <c r="E172" s="38"/>
+      <c r="F172" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G172" s="37"/>
+      <c r="H172" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="I172" s="38"/>
+      <c r="J172" s="38"/>
+    </row>
+    <row r="173" spans="1:10" ht="17">
+      <c r="A173" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" s="37"/>
+      <c r="C173" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D173" s="38"/>
+      <c r="E173" s="38"/>
+      <c r="F173" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G173" s="37"/>
+      <c r="H173" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I173" s="38"/>
+      <c r="J173" s="38"/>
+    </row>
+    <row r="174" spans="1:10" ht="17">
+      <c r="A174" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B174" s="37"/>
+      <c r="C174" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="D174" s="38"/>
+      <c r="E174" s="38"/>
+      <c r="F174" s="38"/>
+      <c r="G174" s="38"/>
+      <c r="H174" s="38"/>
+      <c r="I174" s="38"/>
+      <c r="J174" s="38"/>
+    </row>
+    <row r="175" spans="1:10" ht="17">
+      <c r="A175" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B175" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C175" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D175" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E175" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G175" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H175" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I175" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J175" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="17">
+      <c r="A176" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B176" s="19"/>
+      <c r="C176" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D176" s="19"/>
+      <c r="E176" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F176" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G176" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H176" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I176" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J176" s="19"/>
+    </row>
+    <row r="177" spans="1:10" ht="17">
+      <c r="A177" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177" s="19"/>
+      <c r="C177" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D177" s="19">
+        <v>16</v>
+      </c>
+      <c r="E177" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F177" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G177" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H177" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I177" s="19"/>
+      <c r="J177" s="19"/>
+    </row>
+    <row r="178" spans="1:10" ht="17">
+      <c r="A178" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B178" s="19"/>
+      <c r="C178" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D178" s="19">
+        <v>255</v>
+      </c>
+      <c r="E178" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F178" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G178" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H178" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I178" s="19"/>
+      <c r="J178" s="19"/>
+    </row>
+    <row r="179" spans="1:10" ht="17">
+      <c r="A179" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B179" s="19"/>
+      <c r="C179" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D179" s="19"/>
+      <c r="E179" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F179" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G179" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H179" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I179" s="19"/>
+      <c r="J179" s="19"/>
+    </row>
+    <row r="180" spans="1:10" ht="17">
+      <c r="A180" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180" s="19"/>
+      <c r="C180" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D180" s="19">
+        <v>6</v>
+      </c>
+      <c r="E180" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F180" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G180" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H180" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I180" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J180" s="19"/>
+    </row>
+    <row r="181" spans="1:10" ht="17">
+      <c r="A181" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B181" s="19"/>
+      <c r="C181" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D181" s="19">
+        <v>6</v>
+      </c>
+      <c r="E181" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F181" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G181" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H181" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I181" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J181" s="19"/>
+    </row>
+    <row r="183" spans="1:10" ht="17">
+      <c r="A183" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B183" s="37"/>
+      <c r="C183" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="D183" s="38"/>
+      <c r="E183" s="38"/>
+      <c r="F183" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G183" s="37"/>
+      <c r="H183" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="I183" s="38"/>
+      <c r="J183" s="38"/>
+    </row>
+    <row r="184" spans="1:10" ht="17">
+      <c r="A184" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" s="37"/>
+      <c r="C184" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="D184" s="38"/>
+      <c r="E184" s="38"/>
+      <c r="F184" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G184" s="37"/>
+      <c r="H184" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="I184" s="38"/>
+      <c r="J184" s="38"/>
+    </row>
+    <row r="185" spans="1:10" ht="17">
+      <c r="A185" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B185" s="37"/>
+      <c r="C185" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="D185" s="38"/>
+      <c r="E185" s="38"/>
+      <c r="F185" s="38"/>
+      <c r="G185" s="38"/>
+      <c r="H185" s="38"/>
+      <c r="I185" s="38"/>
+      <c r="J185" s="38"/>
+    </row>
+    <row r="186" spans="1:10" ht="17">
+      <c r="A186" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B186" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C186" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D186" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E186" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F186" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G186" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H186" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I186" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J186" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="17">
+      <c r="A187" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B187" s="19"/>
+      <c r="C187" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D187" s="19"/>
+      <c r="E187" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F187" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G187" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H187" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I187" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J187" s="19"/>
+    </row>
+    <row r="188" spans="1:10" ht="17">
+      <c r="A188" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B188" s="19"/>
+      <c r="C188" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D188" s="19"/>
+      <c r="E188" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F188" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G188" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H188" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I188" s="19"/>
+      <c r="J188" s="19"/>
+    </row>
+    <row r="189" spans="1:10" ht="17">
+      <c r="A189" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B189" s="19"/>
+      <c r="C189" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D189" s="19">
+        <v>16</v>
+      </c>
+      <c r="E189" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F189" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G189" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H189" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I189" s="19"/>
+      <c r="J189" s="19"/>
+    </row>
+    <row r="190" spans="1:10" ht="17">
+      <c r="A190" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B190" s="19"/>
+      <c r="C190" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D190" s="19">
+        <v>100</v>
+      </c>
+      <c r="E190" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F190" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G190" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H190" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I190" s="19"/>
+      <c r="J190" s="19"/>
+    </row>
+    <row r="191" spans="1:10" ht="17">
+      <c r="A191" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B191" s="19"/>
+      <c r="C191" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D191" s="19"/>
+      <c r="E191" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G191" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H191" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I191" s="19"/>
+      <c r="J191" s="19"/>
+    </row>
+    <row r="192" spans="1:10" ht="17">
+      <c r="A192" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B192" s="19"/>
+      <c r="C192" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D192" s="19">
+        <v>6</v>
+      </c>
+      <c r="E192" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F192" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G192" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H192" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I192" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J192" s="19"/>
+    </row>
+    <row r="193" spans="1:10" ht="17">
+      <c r="A193" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B193" s="19"/>
+      <c r="C193" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D193" s="19">
+        <v>10</v>
+      </c>
+      <c r="E193" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F193" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G193" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H193" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I193" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="J193" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="117">
+    <mergeCell ref="A4:J5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="C7:E7"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A4:J5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="A8:J28"/>
-    <mergeCell ref="A29:J30"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="F31:J31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A8:M56"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:J62"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="F59:J59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:J83"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="F80:J80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:J94"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="H92:J92"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="H111:J111"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="C112:J112"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="H110:J110"/>
+    <mergeCell ref="A150:B150"/>
+    <mergeCell ref="C150:J150"/>
+    <mergeCell ref="A148:B148"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="H148:J148"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="H121:J121"/>
+    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="H149:J149"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="C132:J132"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="C122:J122"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="H130:J130"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="H160:J160"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="C161:J161"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="H159:J159"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="H173:J173"/>
+    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="C174:J174"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="H172:J172"/>
+    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="F184:G184"/>
+    <mergeCell ref="H184:J184"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="C185:J185"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="F183:G183"/>
+    <mergeCell ref="H183:J183"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2322,65 +6656,65 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J46"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="10" max="10" width="5.5234375" customWidth="1"/>
+    <col min="10" max="10" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.7" thickBot="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
+      <c r="A1" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="75"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="6" customHeight="1"/>
     <row r="4" spans="1:10">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="22"/>
@@ -2395,74 +6729,74 @@
       <c r="J6" s="23"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="23"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="65" t="s">
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="65" t="s">
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="65" t="s">
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="65"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="65"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="21"/>
@@ -2477,466 +6811,466 @@
       <c r="J12" s="21"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="66"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="65" t="s">
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="64" t="s">
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="64" t="s">
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="64" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="64" t="s">
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="65" t="s">
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="64" t="s">
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="64" t="s">
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="64" t="s">
+      <c r="B22" s="71"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="64" t="s">
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="64" t="s">
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="64" t="s">
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="64" t="s">
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="64" t="s">
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="64" t="s">
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="64"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="64" t="s">
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="64"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="64" t="s">
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="64" t="s">
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="64" t="s">
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="64" t="s">
+      <c r="B33" s="71"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="64" t="s">
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="64" t="s">
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="64" t="s">
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="64" t="s">
+      <c r="B37" s="71"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="64" t="s">
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="64" t="s">
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="64" t="s">
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="64" t="s">
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="64"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="64" t="s">
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="64" t="s">
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="64"/>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="64"/>
-      <c r="J43" s="64"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="64" t="s">
+      <c r="B44" s="71"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="71"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="64"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="64"/>
-      <c r="C45" s="64"/>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
-      <c r="I45" s="64"/>
-      <c r="J45" s="64"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="71"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="24"/>
